--- a/design/templates/generated/North_Central/PADDY_FLOOD_NCE_V1_upload_template.xlsx
+++ b/design/templates/generated/North_Central/PADDY_FLOOD_NCE_V1_upload_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2020-2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2021-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-2030" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEIGHTS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_META" sheetId="5" state="hidden" r:id="rId5"/>
@@ -562,7 +562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2020-2025 - Agriculture Sector / Paddy - Flood - North Central Province   [profile PADDY_FLOOD_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2021-2025 - Agriculture Sector / Paddy - Flood - North Central Province   [profile PADDY_FLOOD_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2025</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="U4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2020-2025</t>
+          <t>Dept. report 2021-2025</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
@@ -886,7 +886,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>NCE-001</t>
+          <t>AN1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2025</v>
@@ -926,7 +926,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>NCE-002</t>
+          <t>AN2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2025</v>
@@ -966,7 +966,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NCE-003</t>
+          <t>AN3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2025</v>
@@ -1006,7 +1006,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>NCE-004</t>
+          <t>AN4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2025</v>
@@ -1046,7 +1046,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NCE-005</t>
+          <t>AN5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2025</v>
@@ -1086,7 +1086,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NCE-006</t>
+          <t>AN6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2025</v>
@@ -1126,7 +1126,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>NCE-007</t>
+          <t>AN7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2025</v>
@@ -1166,7 +1166,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NCE-008</t>
+          <t>AN8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2025</v>
@@ -1206,7 +1206,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>NCE-009</t>
+          <t>AN9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2025</v>
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NCE-010</t>
+          <t>AN10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2025</v>
@@ -1286,7 +1286,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NCE-011</t>
+          <t>AN11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2025</v>
@@ -1326,7 +1326,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NCE-012</t>
+          <t>AN12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2025</v>
@@ -1366,7 +1366,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NCE-013</t>
+          <t>AN13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2025</v>
@@ -1406,7 +1406,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NCE-014</t>
+          <t>AN14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2025</v>
@@ -1446,7 +1446,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>NCE-015</t>
+          <t>AN15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2025</v>
@@ -1486,7 +1486,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NCE-016</t>
+          <t>AN16</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2025</v>
@@ -1526,7 +1526,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NCE-017</t>
+          <t>AN17</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2025</v>
@@ -1566,7 +1566,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NCE-018</t>
+          <t>AN18</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2025</v>
@@ -1606,7 +1606,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NCE-019</t>
+          <t>AN19</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2025</v>
@@ -1646,7 +1646,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>NCE-020</t>
+          <t>AN20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2025</v>
@@ -1686,7 +1686,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NCE-021</t>
+          <t>AN21</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2025</v>
@@ -1726,7 +1726,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>NCE-022</t>
+          <t>AN22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2025</v>
@@ -1766,7 +1766,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NCE-023</t>
+          <t>PO1</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2025</v>
@@ -1806,7 +1806,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NCE-024</t>
+          <t>PO2</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2025</v>
@@ -1846,7 +1846,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>NCE-025</t>
+          <t>PO3</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2025</v>
@@ -1886,7 +1886,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NCE-026</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2025</v>
@@ -1926,7 +1926,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>NCE-027</t>
+          <t>PO5</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2025</v>
@@ -1966,7 +1966,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NCE-028</t>
+          <t>PO6</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2025</v>
@@ -2006,7 +2006,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>NCE-029</t>
+          <t>PO7</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2025</v>
@@ -2044,7 +2044,6 @@
       <c r="V33" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
@@ -2093,7 +2092,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2025-2030 - Agriculture Sector / Paddy - Flood - North Central Province   [profile PADDY_FLOOD_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2026-2030 - Agriculture Sector / Paddy - Flood - North Central Province   [profile PADDY_FLOOD_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2352,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2030</v>
@@ -2405,7 +2404,7 @@
       </c>
       <c r="U4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2025-2030</t>
+          <t>Dept. report 2026-2030</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
@@ -2417,7 +2416,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>NCE-001</t>
+          <t>AN1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -2431,7 +2430,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2030</v>
@@ -2457,7 +2456,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>NCE-002</t>
+          <t>AN2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2471,7 +2470,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2030</v>
@@ -2497,7 +2496,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NCE-003</t>
+          <t>AN3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -2511,7 +2510,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2030</v>
@@ -2537,7 +2536,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>NCE-004</t>
+          <t>AN4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2551,7 +2550,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2030</v>
@@ -2577,7 +2576,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NCE-005</t>
+          <t>AN5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -2591,7 +2590,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2030</v>
@@ -2617,7 +2616,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NCE-006</t>
+          <t>AN6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -2631,7 +2630,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2030</v>
@@ -2657,7 +2656,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>NCE-007</t>
+          <t>AN7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -2671,7 +2670,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2030</v>
@@ -2697,7 +2696,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NCE-008</t>
+          <t>AN8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -2711,7 +2710,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2030</v>
@@ -2737,7 +2736,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>NCE-009</t>
+          <t>AN9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -2751,7 +2750,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2030</v>
@@ -2777,7 +2776,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NCE-010</t>
+          <t>AN10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -2791,7 +2790,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2030</v>
@@ -2817,7 +2816,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NCE-011</t>
+          <t>AN11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -2831,7 +2830,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2030</v>
@@ -2857,7 +2856,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NCE-012</t>
+          <t>AN12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -2871,7 +2870,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2030</v>
@@ -2897,7 +2896,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NCE-013</t>
+          <t>AN13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -2911,7 +2910,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2030</v>
@@ -2937,7 +2936,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NCE-014</t>
+          <t>AN14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -2951,7 +2950,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2030</v>
@@ -2977,7 +2976,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>NCE-015</t>
+          <t>AN15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -2991,7 +2990,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2030</v>
@@ -3017,7 +3016,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NCE-016</t>
+          <t>AN16</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -3031,7 +3030,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2030</v>
@@ -3057,7 +3056,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NCE-017</t>
+          <t>AN17</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -3071,7 +3070,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2030</v>
@@ -3097,7 +3096,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NCE-018</t>
+          <t>AN18</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -3111,7 +3110,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2030</v>
@@ -3137,7 +3136,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NCE-019</t>
+          <t>AN19</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -3151,7 +3150,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2030</v>
@@ -3177,7 +3176,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>NCE-020</t>
+          <t>AN20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -3191,7 +3190,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2030</v>
@@ -3217,7 +3216,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NCE-021</t>
+          <t>AN21</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -3231,7 +3230,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2030</v>
@@ -3257,7 +3256,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>NCE-022</t>
+          <t>AN22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -3271,7 +3270,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2030</v>
@@ -3297,7 +3296,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NCE-023</t>
+          <t>PO1</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -3311,7 +3310,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2030</v>
@@ -3337,7 +3336,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NCE-024</t>
+          <t>PO2</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -3351,7 +3350,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2030</v>
@@ -3377,7 +3376,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>NCE-025</t>
+          <t>PO3</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -3391,7 +3390,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2030</v>
@@ -3417,7 +3416,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NCE-026</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -3431,7 +3430,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2030</v>
@@ -3457,7 +3456,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>NCE-027</t>
+          <t>PO5</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -3471,7 +3470,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2030</v>
@@ -3497,7 +3496,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NCE-028</t>
+          <t>PO6</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -3511,7 +3510,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2030</v>
@@ -3537,7 +3536,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>NCE-029</t>
+          <t>PO7</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -3551,7 +3550,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2030</v>
@@ -3575,7 +3574,6 @@
       <c r="V33" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
@@ -3594,7 +3592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3603,6 +3601,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3650,6 +3649,11 @@
           <t>PROPOSED WEIGHT % (read at import)</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>basis of the proposal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -3670,6 +3674,7 @@
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="12" t="n"/>
+      <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -3698,6 +3703,7 @@
       <c r="F5" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="G5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -3718,6 +3724,7 @@
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="12" t="n"/>
+      <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -3738,6 +3745,7 @@
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
+      <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -3758,6 +3766,7 @@
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
+      <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -3786,6 +3795,7 @@
       <c r="F9" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="G9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -3814,6 +3824,7 @@
       <c r="F10" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -3842,6 +3853,7 @@
       <c r="F11" s="12" t="n">
         <v>25</v>
       </c>
+      <c r="G11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -3870,6 +3882,7 @@
       <c r="F12" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -3890,6 +3903,7 @@
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
+      <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -3918,6 +3932,7 @@
       <c r="F14" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="G14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -3946,6 +3961,7 @@
       <c r="F15" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -3974,6 +3990,7 @@
       <c r="F16" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -4002,6 +4019,7 @@
       <c r="F17" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -4022,6 +4040,7 @@
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="12" t="n"/>
+      <c r="G18" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
@@ -4046,9 +4065,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
@@ -4087,14 +4105,14 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: PADDY_FLOOD_NCE_V1   |   generated 2026-07-29 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: PADDY_FLOOD_NCE_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>1. One tab per data period (2020-2025, 2025-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
+          <t>1. One tab per data period (2021-2025, 2026-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
         </is>
       </c>
     </row>
@@ -4108,14 +4126,14 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2b. The year 2025 appears in both tabs. If a year sits in two periods the system uses the LATER period's value, so nothing is counted twice.</t>
+          <t>2b. The two periods are contiguous and do not overlap (changed 2026-09-03 at the Central panel's request - the old 2020-2025 / 2025-2030 pair shared the year 2025 and needed a tie-break). Every year belongs to exactly one tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>3. Edit ONLY the yellow cells. Division codes, names, district and the period columns are pre-filled and locked.</t>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4147,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Do not add, remove, rename or reorder columns or tabs. Files with changed structure are rejected on import.</t>
+          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4713,80 +4731,104 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>generated</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>unlocked-review</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dsd_level</t>
+          <t>panel_overrides</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>DS_DIVISION</t>
+          <t>0 add, 0 retire</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>periods</t>
+          <t>generated</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2020-2025|2025-2030</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>n_variables</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>15</v>
+          <t>dsd_level</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>DS_DIVISION</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>period_rule_default</t>
+          <t>periods</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>average (typical year); 2025 -&gt; latest period wins</t>
+          <t>2021-2025|2026-2030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>period_aggregation</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|ANNUAL_AVERAGE_RAINFALL=average|ASWEDDUMIZED_PADDY_EXTENT=average|HARVESTED_PADDY_EXTENT_YALA_MAHA=average|PADDY_FARMERS=average|PADDY_PRODUCTION_MT_MAHA_YALA=average|PCT_FOREST_COVER=average|PCT_PADDY_FARMERS_AGRICULTURAL_OPERATORS=average|PCT_PADDY_LAND_TOTAL_LAND_AREA=average|PCT_WATER_SURFACE_AREA=average|WATER_SURFACE_AREA=average</t>
-        </is>
+          <t>n_variables</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
+          <t>period_rule_default</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>average (typical year); periods are contiguous, no overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>period_aggregation</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|ANNUAL_AVERAGE_RAINFALL=average|ASWEDDUMIZED_PADDY_EXTENT=average|HARVESTED_PADDY_EXTENT_YALA_MAHA=average|PADDY_FARMERS=average|PADDY_PRODUCTION_MT_MAHA_YALA=average|PCT_FOREST_COVER=average|PCT_PADDY_FARMERS_AGRICULTURAL_OPERATORS=average|PCT_PADDY_LAND_TOTAL_LAND_AREA=average|PCT_WATER_SURFACE_AREA=average|WATER_SURFACE_AREA=average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>expected_columns</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|FLOOD_EVENTS_1974_TO_2023|FLOOD_HAZARD_INDEX|LIGHTNING_INCIDENTS_1974_TO_2023|STRONG_WIND_EVENTS_1978_TO_2023|VERY_WET_DAYS|ANNUAL_AVERAGE_RAINFALL|ASWEDDUMIZED_PADDY_EXTENT|HARVESTED_PADDY_EXTENT_YALA_MAHA|PADDY_FARMERS|PADDY_PRODUCTION_MT_MAHA_YALA|PCT_FOREST_COVER|PCT_PADDY_FARMERS_AGRICULTURAL_OPERATORS|PCT_PADDY_LAND_TOTAL_LAND_AREA|PCT_WATER_SURFACE_AREA|WATER_SURFACE_AREA|DATA_SOURCE|NOTES</t>
         </is>

--- a/design/templates/generated/North_Central/PADDY_FLOOD_NCE_V1_upload_template.xlsx
+++ b/design/templates/generated/North_Central/PADDY_FLOOD_NCE_V1_upload_template.xlsx
@@ -4105,7 +4105,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: PADDY_FLOOD_NCE_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: PADDY_FLOOD_NCE_V1   |   generated 2026-09-14 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
@@ -4131,9 +4131,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>3. The yellow cells are where data belongs. Division codes, names, district and the period columns are pre-filled - change one only to correct a genuine error. Nothing in this file is protected, so please treat that as the instruction it is; the importer checks those columns and will refuse what it cannot match.</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
+          <t>5. Do not add, remove, rename or reorder columns or tabs. Excel will now let you - the sheet is not protected - but the importer will not: the hidden _META tab states this file's column contract and a file whose structure has changed is refused, naming what changed. Nothing loads partially, so a rejected file loads nothing at all.</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>unlocked-review</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
